--- a/StructureDefinition-access-check-eligibility-in.xlsx
+++ b/StructureDefinition-access-check-eligibility-in.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.7.0</t>
+    <t>0.9.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-26T23:16:42-05:00</t>
+    <t>2026-03-06T16:03:26-05:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -647,7 +647,7 @@
     <t>required</t>
   </si>
   <si>
-    <t>https://globalalliantinc.com/access/ValueSet/ACCESSTrackVS|0.7.0</t>
+    <t>https://globalalliantinc.com/access/ValueSet/ACCESSTrackVS|0.9.0</t>
   </si>
   <si>
     <t>Parameters.parameter:track.resource</t>
@@ -656,31 +656,31 @@
     <t>Parameters.parameter:track.part</t>
   </si>
   <si>
-    <t>Parameters.parameter:conditions</t>
-  </si>
-  <si>
-    <t>conditions</t>
-  </si>
-  <si>
-    <t>Parameters.parameter:conditions.id</t>
-  </si>
-  <si>
-    <t>Parameters.parameter:conditions.extension</t>
-  </si>
-  <si>
-    <t>Parameters.parameter:conditions.modifierExtension</t>
-  </si>
-  <si>
-    <t>Parameters.parameter:conditions.name</t>
-  </si>
-  <si>
-    <t>Parameters.parameter:conditions.value[x]</t>
-  </si>
-  <si>
-    <t>Parameters.parameter:conditions.resource</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Condition {https://globalalliantinc.com/access/StructureDefinition/access-condition|0.7.0}
+    <t>Parameters.parameter:condition</t>
+  </si>
+  <si>
+    <t>condition</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:condition.id</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:condition.extension</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:condition.modifierExtension</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:condition.name</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:condition.value[x]</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:condition.resource</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Condition {https://globalalliantinc.com/access/StructureDefinition/access-condition|0.9.0}
 </t>
   </si>
   <si>
@@ -693,7 +693,7 @@
     <t>Observation[classCode=OBS, moodCode=EVN, code=ASSERTION, value&lt;Diagnosis]</t>
   </si>
   <si>
-    <t>Parameters.parameter:conditions.part</t>
+    <t>Parameters.parameter:condition.part</t>
   </si>
 </sst>
 </file>
@@ -3218,7 +3218,7 @@
         <v>76</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>75</v>
@@ -4074,7 +4074,7 @@
         <v>76</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>75</v>
@@ -4824,7 +4824,7 @@
         <v>76</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>75</v>
@@ -5784,7 +5784,7 @@
         <v>76</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>75</v>
@@ -6534,7 +6534,7 @@
         <v>76</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>75</v>

--- a/StructureDefinition-access-check-eligibility-in.xlsx
+++ b/StructureDefinition-access-check-eligibility-in.xlsx
@@ -27,13 +27,13 @@
     <t>URL</t>
   </si>
   <si>
-    <t>https://globalalliantinc.com/access/StructureDefinition/access-check-eligibility-in</t>
+    <t>https://dsacms.github.io/cmmi-access-model/StructureDefinition/access-check-eligibility-in</t>
   </si>
   <si>
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.0</t>
+    <t>0.9.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-06T16:03:26-05:00</t>
+    <t>2026-03-12T23:55:37-07:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -647,7 +647,7 @@
     <t>required</t>
   </si>
   <si>
-    <t>https://globalalliantinc.com/access/ValueSet/ACCESSTrackVS|0.9.0</t>
+    <t>https://dsacms.github.io/cmmi-access-model/ValueSet/ACCESSTrackVS|0.9.1</t>
   </si>
   <si>
     <t>Parameters.parameter:track.resource</t>
@@ -680,7 +680,7 @@
     <t>Parameters.parameter:condition.resource</t>
   </si>
   <si>
-    <t xml:space="preserve">Condition {https://globalalliantinc.com/access/StructureDefinition/access-condition|0.9.0}
+    <t xml:space="preserve">Condition {https://dsacms.github.io/cmmi-access-model/StructureDefinition/access-condition|0.9.1}
 </t>
   </si>
   <si>
@@ -1038,7 +1038,7 @@
     <col min="23" max="23" width="15.01171875" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="14.62890625" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="17.08203125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="53.0625" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="61.64453125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.07421875" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="17.98046875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="16.2578125" customWidth="true" bestFit="true"/>

--- a/StructureDefinition-access-check-eligibility-in.xlsx
+++ b/StructureDefinition-access-check-eligibility-in.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1851" uniqueCount="218">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1850" uniqueCount="217">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.1</t>
+    <t>0.9.6</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-12T23:55:37-07:00</t>
+    <t>2026-04-24T13:45:33-04:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -351,9 +351,6 @@
     <t>preferred</t>
   </si>
   <si>
-    <t>A human language.</t>
-  </si>
-  <si>
     <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
@@ -539,7 +536,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-access-participant-id-pattern:ACCESS Participant ID must follow the pattern ACCESS#### where #### represents exactly 4 digits (e.g., ACCESS0001, ACCESS1234) {value.matches('^ACCESS\\d{4}$')}</t>
+access-participant-id-pattern:ACCESS Participant ID must follow the pattern ACCES##### where ##### represents exactly 5 digits (e.g., ACCES00001, ACCES12345) {value.matches('^ACCES\\d{5}$')}</t>
   </si>
   <si>
     <t>Parameters.parameter:participantID.resource</t>
@@ -647,7 +644,7 @@
     <t>required</t>
   </si>
   <si>
-    <t>https://dsacms.github.io/cmmi-access-model/ValueSet/ACCESSTrackVS|0.9.1</t>
+    <t>https://dsacms.github.io/cmmi-access-model/ValueSet/ACCESSTrackVS|0.9.6</t>
   </si>
   <si>
     <t>Parameters.parameter:track.resource</t>
@@ -680,7 +677,7 @@
     <t>Parameters.parameter:condition.resource</t>
   </si>
   <si>
-    <t xml:space="preserve">Condition {https://dsacms.github.io/cmmi-access-model/StructureDefinition/access-condition|0.9.1}
+    <t xml:space="preserve">Condition {https://dsacms.github.io/cmmi-access-model/StructureDefinition/access-condition|0.9.6}
 </t>
   </si>
   <si>
@@ -1663,29 +1660,27 @@
       <c r="X6" t="s" s="2">
         <v>108</v>
       </c>
-      <c r="Y6" t="s" s="2">
+      <c r="Y6" s="2"/>
+      <c r="Z6" t="s" s="2">
         <v>109</v>
       </c>
-      <c r="Z6" t="s" s="2">
+      <c r="AA6" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB6" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC6" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD6" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE6" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF6" t="s" s="2">
         <v>110</v>
-      </c>
-      <c r="AA6" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB6" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC6" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD6" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE6" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF6" t="s" s="2">
-        <v>111</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>76</v>
@@ -1708,10 +1703,10 @@
     </row>
     <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
@@ -1719,7 +1714,7 @@
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="G7" t="s" s="2">
         <v>77</v>
@@ -1734,13 +1729,13 @@
         <v>85</v>
       </c>
       <c r="K7" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="L7" t="s" s="2">
         <v>114</v>
       </c>
-      <c r="L7" t="s" s="2">
+      <c r="M7" t="s" s="2">
         <v>115</v>
-      </c>
-      <c r="M7" t="s" s="2">
-        <v>116</v>
       </c>
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
@@ -1779,17 +1774,17 @@
         <v>75</v>
       </c>
       <c r="AB7" t="s" s="2">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="AC7" s="2"/>
       <c r="AD7" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE7" t="s" s="2">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>76</v>
@@ -1801,7 +1796,7 @@
         <v>75</v>
       </c>
       <c r="AJ7" t="s" s="2">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="AK7" t="s" s="2">
         <v>75</v>
@@ -1812,10 +1807,10 @@
     </row>
     <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
@@ -1838,13 +1833,13 @@
         <v>75</v>
       </c>
       <c r="K8" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="L8" t="s" s="2">
         <v>121</v>
       </c>
-      <c r="L8" t="s" s="2">
+      <c r="M8" t="s" s="2">
         <v>122</v>
-      </c>
-      <c r="M8" t="s" s="2">
-        <v>123</v>
       </c>
       <c r="N8" s="2"/>
       <c r="O8" s="2"/>
@@ -1895,7 +1890,7 @@
         <v>75</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>76</v>
@@ -1918,14 +1913,14 @@
     </row>
     <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
@@ -1944,16 +1939,16 @@
         <v>75</v>
       </c>
       <c r="K9" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="L9" t="s" s="2">
         <v>127</v>
       </c>
-      <c r="L9" t="s" s="2">
+      <c r="M9" t="s" s="2">
         <v>128</v>
       </c>
-      <c r="M9" t="s" s="2">
+      <c r="N9" t="s" s="2">
         <v>129</v>
-      </c>
-      <c r="N9" t="s" s="2">
-        <v>130</v>
       </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
@@ -2003,7 +1998,7 @@
         <v>75</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>76</v>
@@ -2015,7 +2010,7 @@
         <v>75</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>75</v>
@@ -2026,14 +2021,14 @@
     </row>
     <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
@@ -2052,19 +2047,19 @@
         <v>85</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="L10" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="M10" t="s" s="2">
         <v>135</v>
       </c>
-      <c r="M10" t="s" s="2">
+      <c r="N10" t="s" s="2">
+        <v>129</v>
+      </c>
+      <c r="O10" t="s" s="2">
         <v>136</v>
-      </c>
-      <c r="N10" t="s" s="2">
-        <v>130</v>
-      </c>
-      <c r="O10" t="s" s="2">
-        <v>137</v>
       </c>
       <c r="P10" t="s" s="2">
         <v>75</v>
@@ -2113,7 +2108,7 @@
         <v>75</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>76</v>
@@ -2125,21 +2120,21 @@
         <v>75</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL10" t="s" s="2">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -2162,13 +2157,13 @@
         <v>85</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="L11" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="M11" t="s" s="2">
         <v>141</v>
-      </c>
-      <c r="M11" t="s" s="2">
-        <v>142</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -2219,7 +2214,7 @@
         <v>75</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>84</v>
@@ -2242,10 +2237,10 @@
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2268,13 +2263,13 @@
         <v>85</v>
       </c>
       <c r="K12" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="L12" t="s" s="2">
         <v>144</v>
       </c>
-      <c r="L12" t="s" s="2">
+      <c r="M12" t="s" s="2">
         <v>145</v>
-      </c>
-      <c r="M12" t="s" s="2">
-        <v>146</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -2325,7 +2320,7 @@
         <v>75</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>76</v>
@@ -2334,7 +2329,7 @@
         <v>84</v>
       </c>
       <c r="AI12" t="s" s="2">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="AJ12" t="s" s="2">
         <v>96</v>
@@ -2348,10 +2343,10 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2374,16 +2369,16 @@
         <v>85</v>
       </c>
       <c r="K13" t="s" s="2">
+        <v>148</v>
+      </c>
+      <c r="L13" t="s" s="2">
         <v>149</v>
       </c>
-      <c r="L13" t="s" s="2">
+      <c r="M13" t="s" s="2">
         <v>150</v>
       </c>
-      <c r="M13" t="s" s="2">
+      <c r="N13" t="s" s="2">
         <v>151</v>
-      </c>
-      <c r="N13" t="s" s="2">
-        <v>152</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -2433,7 +2428,7 @@
         <v>75</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>76</v>
@@ -2442,7 +2437,7 @@
         <v>84</v>
       </c>
       <c r="AI13" t="s" s="2">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="AJ13" t="s" s="2">
         <v>75</v>
@@ -2456,10 +2451,10 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2485,13 +2480,13 @@
         <v>75</v>
       </c>
       <c r="L14" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="M14" t="s" s="2">
         <v>154</v>
       </c>
-      <c r="M14" t="s" s="2">
+      <c r="N14" t="s" s="2">
         <v>155</v>
-      </c>
-      <c r="N14" t="s" s="2">
-        <v>156</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -2541,7 +2536,7 @@
         <v>75</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>76</v>
@@ -2564,13 +2559,13 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="B15" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="C15" t="s" s="2">
         <v>157</v>
-      </c>
-      <c r="B15" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="C15" t="s" s="2">
-        <v>158</v>
       </c>
       <c r="D15" t="s" s="2">
         <v>75</v>
@@ -2592,13 +2587,13 @@
         <v>85</v>
       </c>
       <c r="K15" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="L15" t="s" s="2">
         <v>114</v>
       </c>
-      <c r="L15" t="s" s="2">
+      <c r="M15" t="s" s="2">
         <v>115</v>
-      </c>
-      <c r="M15" t="s" s="2">
-        <v>116</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -2649,7 +2644,7 @@
         <v>75</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>76</v>
@@ -2661,7 +2656,7 @@
         <v>75</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="AK15" t="s" s="2">
         <v>75</v>
@@ -2672,10 +2667,10 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -2698,13 +2693,13 @@
         <v>75</v>
       </c>
       <c r="K16" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="L16" t="s" s="2">
         <v>121</v>
       </c>
-      <c r="L16" t="s" s="2">
+      <c r="M16" t="s" s="2">
         <v>122</v>
-      </c>
-      <c r="M16" t="s" s="2">
-        <v>123</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -2755,7 +2750,7 @@
         <v>75</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>76</v>
@@ -2778,14 +2773,14 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
@@ -2804,16 +2799,16 @@
         <v>75</v>
       </c>
       <c r="K17" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="L17" t="s" s="2">
         <v>127</v>
       </c>
-      <c r="L17" t="s" s="2">
+      <c r="M17" t="s" s="2">
         <v>128</v>
       </c>
-      <c r="M17" t="s" s="2">
+      <c r="N17" t="s" s="2">
         <v>129</v>
-      </c>
-      <c r="N17" t="s" s="2">
-        <v>130</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -2863,7 +2858,7 @@
         <v>75</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>76</v>
@@ -2875,7 +2870,7 @@
         <v>75</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="AK17" t="s" s="2">
         <v>75</v>
@@ -2886,10 +2881,10 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -2912,13 +2907,13 @@
         <v>85</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="L18" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="M18" t="s" s="2">
         <v>162</v>
-      </c>
-      <c r="M18" t="s" s="2">
-        <v>163</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -2969,7 +2964,7 @@
         <v>75</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>76</v>
@@ -2981,7 +2976,7 @@
         <v>75</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="AK18" t="s" s="2">
         <v>75</v>
@@ -2992,10 +2987,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3018,13 +3013,13 @@
         <v>85</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="L19" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="M19" t="s" s="2">
         <v>141</v>
-      </c>
-      <c r="M19" t="s" s="2">
-        <v>142</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -3033,7 +3028,7 @@
       </c>
       <c r="Q19" s="2"/>
       <c r="R19" t="s" s="2">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="S19" t="s" s="2">
         <v>75</v>
@@ -3075,7 +3070,7 @@
         <v>75</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>84</v>
@@ -3098,10 +3093,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3124,13 +3119,13 @@
         <v>85</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="L20" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="M20" t="s" s="2">
         <v>145</v>
-      </c>
-      <c r="M20" t="s" s="2">
-        <v>146</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -3181,7 +3176,7 @@
         <v>75</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>76</v>
@@ -3190,10 +3185,10 @@
         <v>84</v>
       </c>
       <c r="AI20" t="s" s="2">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="AK20" t="s" s="2">
         <v>75</v>
@@ -3204,10 +3199,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3230,16 +3225,16 @@
         <v>85</v>
       </c>
       <c r="K21" t="s" s="2">
+        <v>148</v>
+      </c>
+      <c r="L21" t="s" s="2">
         <v>149</v>
       </c>
-      <c r="L21" t="s" s="2">
+      <c r="M21" t="s" s="2">
         <v>150</v>
       </c>
-      <c r="M21" t="s" s="2">
+      <c r="N21" t="s" s="2">
         <v>151</v>
-      </c>
-      <c r="N21" t="s" s="2">
-        <v>152</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -3289,7 +3284,7 @@
         <v>75</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>76</v>
@@ -3298,7 +3293,7 @@
         <v>84</v>
       </c>
       <c r="AI21" t="s" s="2">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="AJ21" t="s" s="2">
         <v>75</v>
@@ -3312,10 +3307,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3341,13 +3336,13 @@
         <v>78</v>
       </c>
       <c r="L22" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="M22" t="s" s="2">
         <v>154</v>
       </c>
-      <c r="M22" t="s" s="2">
+      <c r="N22" t="s" s="2">
         <v>155</v>
-      </c>
-      <c r="N22" t="s" s="2">
-        <v>156</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -3397,7 +3392,7 @@
         <v>75</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>76</v>
@@ -3420,13 +3415,13 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="B23" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="C23" t="s" s="2">
         <v>170</v>
-      </c>
-      <c r="B23" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="C23" t="s" s="2">
-        <v>171</v>
       </c>
       <c r="D23" t="s" s="2">
         <v>75</v>
@@ -3448,13 +3443,13 @@
         <v>85</v>
       </c>
       <c r="K23" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="L23" t="s" s="2">
         <v>114</v>
       </c>
-      <c r="L23" t="s" s="2">
+      <c r="M23" t="s" s="2">
         <v>115</v>
-      </c>
-      <c r="M23" t="s" s="2">
-        <v>116</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -3505,7 +3500,7 @@
         <v>75</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>76</v>
@@ -3517,7 +3512,7 @@
         <v>75</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="AK23" t="s" s="2">
         <v>75</v>
@@ -3528,10 +3523,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3554,13 +3549,13 @@
         <v>75</v>
       </c>
       <c r="K24" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="L24" t="s" s="2">
         <v>121</v>
       </c>
-      <c r="L24" t="s" s="2">
+      <c r="M24" t="s" s="2">
         <v>122</v>
-      </c>
-      <c r="M24" t="s" s="2">
-        <v>123</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -3611,7 +3606,7 @@
         <v>75</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>76</v>
@@ -3634,14 +3629,14 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
@@ -3660,16 +3655,16 @@
         <v>75</v>
       </c>
       <c r="K25" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="L25" t="s" s="2">
         <v>127</v>
       </c>
-      <c r="L25" t="s" s="2">
+      <c r="M25" t="s" s="2">
         <v>128</v>
       </c>
-      <c r="M25" t="s" s="2">
+      <c r="N25" t="s" s="2">
         <v>129</v>
-      </c>
-      <c r="N25" t="s" s="2">
-        <v>130</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
@@ -3719,7 +3714,7 @@
         <v>75</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>76</v>
@@ -3731,7 +3726,7 @@
         <v>75</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="AK25" t="s" s="2">
         <v>75</v>
@@ -3742,10 +3737,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -3768,13 +3763,13 @@
         <v>85</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="L26" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="M26" t="s" s="2">
         <v>162</v>
-      </c>
-      <c r="M26" t="s" s="2">
-        <v>163</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -3825,7 +3820,7 @@
         <v>75</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>76</v>
@@ -3837,7 +3832,7 @@
         <v>75</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="AK26" t="s" s="2">
         <v>75</v>
@@ -3848,10 +3843,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -3874,13 +3869,13 @@
         <v>85</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="L27" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="M27" t="s" s="2">
         <v>141</v>
-      </c>
-      <c r="M27" t="s" s="2">
-        <v>142</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -3889,7 +3884,7 @@
       </c>
       <c r="Q27" s="2"/>
       <c r="R27" t="s" s="2">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="S27" t="s" s="2">
         <v>75</v>
@@ -3931,7 +3926,7 @@
         <v>75</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>84</v>
@@ -3954,10 +3949,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -3980,13 +3975,13 @@
         <v>85</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="L28" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="M28" t="s" s="2">
         <v>145</v>
-      </c>
-      <c r="M28" t="s" s="2">
-        <v>146</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -4037,7 +4032,7 @@
         <v>75</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>76</v>
@@ -4046,7 +4041,7 @@
         <v>84</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="AJ28" t="s" s="2">
         <v>96</v>
@@ -4060,10 +4055,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4086,16 +4081,16 @@
         <v>85</v>
       </c>
       <c r="K29" t="s" s="2">
+        <v>148</v>
+      </c>
+      <c r="L29" t="s" s="2">
         <v>149</v>
       </c>
-      <c r="L29" t="s" s="2">
+      <c r="M29" t="s" s="2">
         <v>150</v>
       </c>
-      <c r="M29" t="s" s="2">
+      <c r="N29" t="s" s="2">
         <v>151</v>
-      </c>
-      <c r="N29" t="s" s="2">
-        <v>152</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -4145,7 +4140,7 @@
         <v>75</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>76</v>
@@ -4154,7 +4149,7 @@
         <v>84</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="AJ29" t="s" s="2">
         <v>75</v>
@@ -4168,10 +4163,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4197,13 +4192,13 @@
         <v>78</v>
       </c>
       <c r="L30" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="M30" t="s" s="2">
         <v>154</v>
       </c>
-      <c r="M30" t="s" s="2">
+      <c r="N30" t="s" s="2">
         <v>155</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>156</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -4253,7 +4248,7 @@
         <v>75</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>76</v>
@@ -4276,13 +4271,13 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="B31" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="C31" t="s" s="2">
         <v>179</v>
-      </c>
-      <c r="B31" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="C31" t="s" s="2">
-        <v>180</v>
       </c>
       <c r="D31" t="s" s="2">
         <v>75</v>
@@ -4304,13 +4299,13 @@
         <v>85</v>
       </c>
       <c r="K31" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="L31" t="s" s="2">
         <v>114</v>
       </c>
-      <c r="L31" t="s" s="2">
+      <c r="M31" t="s" s="2">
         <v>115</v>
-      </c>
-      <c r="M31" t="s" s="2">
-        <v>116</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -4361,7 +4356,7 @@
         <v>75</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>76</v>
@@ -4373,7 +4368,7 @@
         <v>75</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="AK31" t="s" s="2">
         <v>75</v>
@@ -4384,10 +4379,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -4410,13 +4405,13 @@
         <v>75</v>
       </c>
       <c r="K32" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="L32" t="s" s="2">
         <v>121</v>
       </c>
-      <c r="L32" t="s" s="2">
+      <c r="M32" t="s" s="2">
         <v>122</v>
-      </c>
-      <c r="M32" t="s" s="2">
-        <v>123</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -4467,7 +4462,7 @@
         <v>75</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>76</v>
@@ -4490,14 +4485,14 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
@@ -4516,16 +4511,16 @@
         <v>75</v>
       </c>
       <c r="K33" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="L33" t="s" s="2">
         <v>127</v>
       </c>
-      <c r="L33" t="s" s="2">
+      <c r="M33" t="s" s="2">
         <v>128</v>
       </c>
-      <c r="M33" t="s" s="2">
+      <c r="N33" t="s" s="2">
         <v>129</v>
-      </c>
-      <c r="N33" t="s" s="2">
-        <v>130</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -4575,7 +4570,7 @@
         <v>75</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>76</v>
@@ -4587,7 +4582,7 @@
         <v>75</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>75</v>
@@ -4598,10 +4593,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -4624,13 +4619,13 @@
         <v>85</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="L34" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="M34" t="s" s="2">
         <v>162</v>
-      </c>
-      <c r="M34" t="s" s="2">
-        <v>163</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -4681,7 +4676,7 @@
         <v>75</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>76</v>
@@ -4693,7 +4688,7 @@
         <v>75</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="AK34" t="s" s="2">
         <v>75</v>
@@ -4704,10 +4699,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -4730,13 +4725,13 @@
         <v>85</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="L35" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="M35" t="s" s="2">
         <v>141</v>
-      </c>
-      <c r="M35" t="s" s="2">
-        <v>142</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -4745,7 +4740,7 @@
       </c>
       <c r="Q35" s="2"/>
       <c r="R35" t="s" s="2">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="S35" t="s" s="2">
         <v>75</v>
@@ -4787,7 +4782,7 @@
         <v>75</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>84</v>
@@ -4810,10 +4805,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -4836,13 +4831,13 @@
         <v>85</v>
       </c>
       <c r="K36" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="L36" t="s" s="2">
         <v>144</v>
       </c>
-      <c r="L36" t="s" s="2">
+      <c r="M36" t="s" s="2">
         <v>145</v>
-      </c>
-      <c r="M36" t="s" s="2">
-        <v>146</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -4893,7 +4888,7 @@
         <v>75</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>76</v>
@@ -4902,7 +4897,7 @@
         <v>84</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="AJ36" t="s" s="2">
         <v>96</v>
@@ -4916,14 +4911,14 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
@@ -4942,16 +4937,16 @@
         <v>75</v>
       </c>
       <c r="K37" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="L37" t="s" s="2">
         <v>188</v>
       </c>
-      <c r="L37" t="s" s="2">
+      <c r="M37" t="s" s="2">
         <v>189</v>
       </c>
-      <c r="M37" t="s" s="2">
-        <v>190</v>
-      </c>
       <c r="N37" t="s" s="2">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
@@ -5001,7 +4996,7 @@
         <v>75</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>76</v>
@@ -5019,15 +5014,15 @@
         <v>75</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5053,13 +5048,13 @@
         <v>78</v>
       </c>
       <c r="L38" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="M38" t="s" s="2">
         <v>154</v>
       </c>
-      <c r="M38" t="s" s="2">
+      <c r="N38" t="s" s="2">
         <v>155</v>
-      </c>
-      <c r="N38" t="s" s="2">
-        <v>156</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -5109,7 +5104,7 @@
         <v>75</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>76</v>
@@ -5132,13 +5127,13 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="B39" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="C39" t="s" s="2">
         <v>193</v>
-      </c>
-      <c r="B39" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="C39" t="s" s="2">
-        <v>194</v>
       </c>
       <c r="D39" t="s" s="2">
         <v>75</v>
@@ -5160,13 +5155,13 @@
         <v>85</v>
       </c>
       <c r="K39" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="L39" t="s" s="2">
         <v>114</v>
       </c>
-      <c r="L39" t="s" s="2">
+      <c r="M39" t="s" s="2">
         <v>115</v>
-      </c>
-      <c r="M39" t="s" s="2">
-        <v>116</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -5217,7 +5212,7 @@
         <v>75</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>76</v>
@@ -5229,7 +5224,7 @@
         <v>75</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>75</v>
@@ -5240,10 +5235,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -5266,13 +5261,13 @@
         <v>75</v>
       </c>
       <c r="K40" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="L40" t="s" s="2">
         <v>121</v>
       </c>
-      <c r="L40" t="s" s="2">
+      <c r="M40" t="s" s="2">
         <v>122</v>
-      </c>
-      <c r="M40" t="s" s="2">
-        <v>123</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -5323,7 +5318,7 @@
         <v>75</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>76</v>
@@ -5346,14 +5341,14 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
@@ -5372,16 +5367,16 @@
         <v>75</v>
       </c>
       <c r="K41" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="L41" t="s" s="2">
         <v>127</v>
       </c>
-      <c r="L41" t="s" s="2">
+      <c r="M41" t="s" s="2">
         <v>128</v>
       </c>
-      <c r="M41" t="s" s="2">
+      <c r="N41" t="s" s="2">
         <v>129</v>
-      </c>
-      <c r="N41" t="s" s="2">
-        <v>130</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -5431,7 +5426,7 @@
         <v>75</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>76</v>
@@ -5443,7 +5438,7 @@
         <v>75</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>75</v>
@@ -5454,10 +5449,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -5480,13 +5475,13 @@
         <v>85</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="L42" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="M42" t="s" s="2">
         <v>162</v>
-      </c>
-      <c r="M42" t="s" s="2">
-        <v>163</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -5537,7 +5532,7 @@
         <v>75</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>76</v>
@@ -5549,7 +5544,7 @@
         <v>75</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>75</v>
@@ -5560,10 +5555,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -5586,13 +5581,13 @@
         <v>85</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="L43" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="M43" t="s" s="2">
         <v>141</v>
-      </c>
-      <c r="M43" t="s" s="2">
-        <v>142</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -5601,7 +5596,7 @@
       </c>
       <c r="Q43" s="2"/>
       <c r="R43" t="s" s="2">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="S43" t="s" s="2">
         <v>75</v>
@@ -5643,7 +5638,7 @@
         <v>75</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>84</v>
@@ -5666,10 +5661,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -5692,13 +5687,13 @@
         <v>85</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="L44" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="M44" t="s" s="2">
         <v>145</v>
-      </c>
-      <c r="M44" t="s" s="2">
-        <v>146</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -5725,11 +5720,11 @@
         <v>75</v>
       </c>
       <c r="X44" t="s" s="2">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="Y44" s="2"/>
       <c r="Z44" t="s" s="2">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>75</v>
@@ -5747,7 +5742,7 @@
         <v>75</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>76</v>
@@ -5756,7 +5751,7 @@
         <v>84</v>
       </c>
       <c r="AI44" t="s" s="2">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="AJ44" t="s" s="2">
         <v>96</v>
@@ -5770,10 +5765,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -5796,16 +5791,16 @@
         <v>85</v>
       </c>
       <c r="K45" t="s" s="2">
+        <v>148</v>
+      </c>
+      <c r="L45" t="s" s="2">
         <v>149</v>
       </c>
-      <c r="L45" t="s" s="2">
+      <c r="M45" t="s" s="2">
         <v>150</v>
       </c>
-      <c r="M45" t="s" s="2">
+      <c r="N45" t="s" s="2">
         <v>151</v>
-      </c>
-      <c r="N45" t="s" s="2">
-        <v>152</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -5855,7 +5850,7 @@
         <v>75</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>76</v>
@@ -5864,7 +5859,7 @@
         <v>84</v>
       </c>
       <c r="AI45" t="s" s="2">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="AJ45" t="s" s="2">
         <v>75</v>
@@ -5878,10 +5873,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -5907,13 +5902,13 @@
         <v>78</v>
       </c>
       <c r="L46" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="M46" t="s" s="2">
         <v>154</v>
       </c>
-      <c r="M46" t="s" s="2">
+      <c r="N46" t="s" s="2">
         <v>155</v>
-      </c>
-      <c r="N46" t="s" s="2">
-        <v>156</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -5963,7 +5958,7 @@
         <v>75</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>76</v>
@@ -5986,13 +5981,13 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
+        <v>204</v>
+      </c>
+      <c r="B47" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="C47" t="s" s="2">
         <v>205</v>
-      </c>
-      <c r="B47" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="C47" t="s" s="2">
-        <v>206</v>
       </c>
       <c r="D47" t="s" s="2">
         <v>75</v>
@@ -6014,13 +6009,13 @@
         <v>85</v>
       </c>
       <c r="K47" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="L47" t="s" s="2">
         <v>114</v>
       </c>
-      <c r="L47" t="s" s="2">
+      <c r="M47" t="s" s="2">
         <v>115</v>
-      </c>
-      <c r="M47" t="s" s="2">
-        <v>116</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -6071,7 +6066,7 @@
         <v>75</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>76</v>
@@ -6083,7 +6078,7 @@
         <v>75</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>75</v>
@@ -6094,10 +6089,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -6120,13 +6115,13 @@
         <v>75</v>
       </c>
       <c r="K48" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="L48" t="s" s="2">
         <v>121</v>
       </c>
-      <c r="L48" t="s" s="2">
+      <c r="M48" t="s" s="2">
         <v>122</v>
-      </c>
-      <c r="M48" t="s" s="2">
-        <v>123</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -6177,7 +6172,7 @@
         <v>75</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>76</v>
@@ -6200,14 +6195,14 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
@@ -6226,16 +6221,16 @@
         <v>75</v>
       </c>
       <c r="K49" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="L49" t="s" s="2">
         <v>127</v>
       </c>
-      <c r="L49" t="s" s="2">
+      <c r="M49" t="s" s="2">
         <v>128</v>
       </c>
-      <c r="M49" t="s" s="2">
+      <c r="N49" t="s" s="2">
         <v>129</v>
-      </c>
-      <c r="N49" t="s" s="2">
-        <v>130</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -6285,7 +6280,7 @@
         <v>75</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>76</v>
@@ -6297,7 +6292,7 @@
         <v>75</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>75</v>
@@ -6308,10 +6303,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -6334,13 +6329,13 @@
         <v>85</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="L50" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="M50" t="s" s="2">
         <v>162</v>
-      </c>
-      <c r="M50" t="s" s="2">
-        <v>163</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -6391,7 +6386,7 @@
         <v>75</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>76</v>
@@ -6403,7 +6398,7 @@
         <v>75</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="AK50" t="s" s="2">
         <v>75</v>
@@ -6414,10 +6409,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -6440,13 +6435,13 @@
         <v>85</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="L51" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="M51" t="s" s="2">
         <v>141</v>
-      </c>
-      <c r="M51" t="s" s="2">
-        <v>142</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -6455,7 +6450,7 @@
       </c>
       <c r="Q51" s="2"/>
       <c r="R51" t="s" s="2">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="S51" t="s" s="2">
         <v>75</v>
@@ -6497,7 +6492,7 @@
         <v>75</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>84</v>
@@ -6520,10 +6515,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -6546,13 +6541,13 @@
         <v>85</v>
       </c>
       <c r="K52" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="L52" t="s" s="2">
         <v>144</v>
       </c>
-      <c r="L52" t="s" s="2">
+      <c r="M52" t="s" s="2">
         <v>145</v>
-      </c>
-      <c r="M52" t="s" s="2">
-        <v>146</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -6603,7 +6598,7 @@
         <v>75</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>76</v>
@@ -6612,7 +6607,7 @@
         <v>84</v>
       </c>
       <c r="AI52" t="s" s="2">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="AJ52" t="s" s="2">
         <v>96</v>
@@ -6626,10 +6621,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -6652,16 +6647,16 @@
         <v>75</v>
       </c>
       <c r="K53" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="L53" t="s" s="2">
         <v>213</v>
       </c>
-      <c r="L53" t="s" s="2">
-        <v>214</v>
-      </c>
       <c r="M53" t="s" s="2">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -6711,7 +6706,7 @@
         <v>75</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>76</v>
@@ -6726,18 +6721,18 @@
         <v>75</v>
       </c>
       <c r="AK53" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="AL53" t="s" s="2">
         <v>215</v>
-      </c>
-      <c r="AL53" t="s" s="2">
-        <v>216</v>
       </c>
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -6763,13 +6758,13 @@
         <v>78</v>
       </c>
       <c r="L54" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="M54" t="s" s="2">
         <v>154</v>
       </c>
-      <c r="M54" t="s" s="2">
+      <c r="N54" t="s" s="2">
         <v>155</v>
-      </c>
-      <c r="N54" t="s" s="2">
-        <v>156</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -6819,7 +6814,7 @@
         <v>75</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>76</v>

--- a/StructureDefinition-access-check-eligibility-in.xlsx
+++ b/StructureDefinition-access-check-eligibility-in.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.6</t>
+    <t>0.9.8</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-24T13:45:33-04:00</t>
+    <t>2026-05-18T15:59:44-04:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -644,7 +644,7 @@
     <t>required</t>
   </si>
   <si>
-    <t>https://dsacms.github.io/cmmi-access-model/ValueSet/ACCESSTrackVS|0.9.6</t>
+    <t>https://dsacms.github.io/cmmi-access-model/ValueSet/ACCESSTrackVS|0.9.8</t>
   </si>
   <si>
     <t>Parameters.parameter:track.resource</t>
@@ -677,7 +677,7 @@
     <t>Parameters.parameter:condition.resource</t>
   </si>
   <si>
-    <t xml:space="preserve">Condition {https://dsacms.github.io/cmmi-access-model/StructureDefinition/access-condition|0.9.6}
+    <t xml:space="preserve">Condition {https://dsacms.github.io/cmmi-access-model/StructureDefinition/access-condition|0.9.8}
 </t>
   </si>
   <si>

--- a/StructureDefinition-access-check-eligibility-in.xlsx
+++ b/StructureDefinition-access-check-eligibility-in.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-18T15:59:44-04:00</t>
+    <t>2026-05-20T09:30:43-04:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-access-check-eligibility-in.xlsx
+++ b/StructureDefinition-access-check-eligibility-in.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AL$54</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AL$62</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1850" uniqueCount="217">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2121" uniqueCount="261">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.8</t>
+    <t>0.9.11</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-20T09:30:43-04:00</t>
+    <t>2026-06-04T22:54:52-04:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -313,13 +313,187 @@
 </t>
   </si>
   <si>
-    <t>Parameters.implicitRules</t>
+    <t>Parameters.meta.id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string
+</t>
+  </si>
+  <si>
+    <t>Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+  </si>
+  <si>
+    <t>Element.id</t>
+  </si>
+  <si>
+    <t>Parameters.meta.extension</t>
+  </si>
+  <si>
+    <t>extensions
+user content</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension
+</t>
+  </si>
+  <si>
+    <t>Additional content defined by implementations</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:url}
+</t>
+  </si>
+  <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
+    <t>Element.extension</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
+  </si>
+  <si>
+    <t>Parameters.meta.versionId</t>
+  </si>
+  <si>
+    <t>Version specific identifier</t>
+  </si>
+  <si>
+    <t>The version specific identifier, as it appears in the version portion of the URL. This value changes when the resource is created, updated, or deleted.</t>
+  </si>
+  <si>
+    <t>The server assigns this value, and ignores what the client specifies, except in the case that the server is imposing version integrity on updates/deletes.</t>
+  </si>
+  <si>
+    <t>Meta.versionId</t>
+  </si>
+  <si>
+    <t>Parameters.meta.lastUpdated</t>
+  </si>
+  <si>
+    <t xml:space="preserve">instant
+</t>
+  </si>
+  <si>
+    <t>When the resource version last changed</t>
+  </si>
+  <si>
+    <t>When the resource last changed - e.g. when the version changed.</t>
+  </si>
+  <si>
+    <t>This value is always populated except when the resource is first being created. The server / resource manager sets this value; what a client provides is irrelevant. This is equivalent to the HTTP Last-Modified and SHOULD have the same value on a [read](http://hl7.org/fhir/R4/http.html#read) interaction.</t>
+  </si>
+  <si>
+    <t>Meta.lastUpdated</t>
+  </si>
+  <si>
+    <t>Parameters.meta.source</t>
   </si>
   <si>
     <t xml:space="preserve">uri
 </t>
   </si>
   <si>
+    <t>Identifies where the resource comes from</t>
+  </si>
+  <si>
+    <t>A uri that identifies the source system of the resource. This provides a minimal amount of [Provenance](http://hl7.org/fhir/R4/provenance.html#) information that can be used to track or differentiate the source of information in the resource. The source may identify another FHIR server, document, message, database, etc.</t>
+  </si>
+  <si>
+    <t>In the provenance resource, this corresponds to Provenance.entity.what[x]. The exact use of the source (and the implied Provenance.entity.role) is left to implementer discretion. Only one nominated source is allowed; for additional provenance details, a full Provenance resource should be used. 
+This element can be used to indicate where the current master source of a resource that has a canonical URL if the resource is no longer hosted at the canonical URL.</t>
+  </si>
+  <si>
+    <t>Meta.source</t>
+  </si>
+  <si>
+    <t>Parameters.meta.profile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">canonical(StructureDefinition|4.0.1)
+</t>
+  </si>
+  <si>
+    <t>Profiles this resource claims to conform to</t>
+  </si>
+  <si>
+    <t>A list of profiles (references to [StructureDefinition](http://hl7.org/fhir/R4/structuredefinition.html#) resources) that this resource claims to conform to. The URL is a reference to [StructureDefinition.url](http://hl7.org/fhir/R4/structuredefinition-definitions.html#StructureDefinition.url).</t>
+  </si>
+  <si>
+    <t>It is up to the server and/or other infrastructure of policy to determine whether/how these claims are verified and/or updated over time.  The list of profile URLs is a set.</t>
+  </si>
+  <si>
+    <t>Meta.profile</t>
+  </si>
+  <si>
+    <t>Parameters.meta.security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coding
+</t>
+  </si>
+  <si>
+    <t>Security Labels applied to this resource</t>
+  </si>
+  <si>
+    <t>Security labels applied to this resource. These tags connect specific resources to the overall security policy and infrastructure.</t>
+  </si>
+  <si>
+    <t>The security labels can be updated without changing the stated version of the resource. The list of security labels is a set. Uniqueness is based the system/code, and version and display are ignored.</t>
+  </si>
+  <si>
+    <t>extensible</t>
+  </si>
+  <si>
+    <t>Security Labels from the Healthcare Privacy and Security Classification System.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/security-labels|4.0.1</t>
+  </si>
+  <si>
+    <t>Meta.security</t>
+  </si>
+  <si>
+    <t>Parameters.meta.tag</t>
+  </si>
+  <si>
+    <t>Tags applied to this resource</t>
+  </si>
+  <si>
+    <t>Tags applied to this resource. Tags are intended to be used to identify and relate resources to process and workflow, and applications are not required to consider the tags when interpreting the meaning of a resource.</t>
+  </si>
+  <si>
+    <t>The tags can be updated without changing the stated version of the resource. The list of tags is a set. Uniqueness is based the system/code, and version and display are ignored.</t>
+  </si>
+  <si>
+    <t>example</t>
+  </si>
+  <si>
+    <t>Codes that represent various types of tags, commonly workflow-related; e.g. "Needs review by Dr. Jones".</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/common-tags|4.0.1</t>
+  </si>
+  <si>
+    <t>Meta.tag</t>
+  </si>
+  <si>
+    <t>Parameters.implicitRules</t>
+  </si>
+  <si>
     <t>A set of rules under which this content was created</t>
   </si>
   <si>
@@ -387,44 +561,7 @@
     <t>Parameters.parameter.id</t>
   </si>
   <si>
-    <t xml:space="preserve">string
-</t>
-  </si>
-  <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
-  </si>
-  <si>
-    <t>Element.id</t>
-  </si>
-  <si>
     <t>Parameters.parameter.extension</t>
-  </si>
-  <si>
-    <t>extensions
-user content</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension
-</t>
-  </si>
-  <si>
-    <t>Additional content defined by implementations</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
-  </si>
-  <si>
-    <t>Element.extension</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
     <t>Parameters.parameter.modifierExtension</t>
@@ -644,7 +781,7 @@
     <t>required</t>
   </si>
   <si>
-    <t>https://dsacms.github.io/cmmi-access-model/ValueSet/ACCESSTrackVS|0.9.8</t>
+    <t>https://dsacms.github.io/cmmi-access-model/ValueSet/ACCESSTrackVS|0.9.11</t>
   </si>
   <si>
     <t>Parameters.parameter:track.resource</t>
@@ -677,7 +814,7 @@
     <t>Parameters.parameter:condition.resource</t>
   </si>
   <si>
-    <t xml:space="preserve">Condition {https://dsacms.github.io/cmmi-access-model/StructureDefinition/access-condition|0.9.8}
+    <t xml:space="preserve">Condition {https://dsacms.github.io/cmmi-access-model/StructureDefinition/access-condition|0.9.11}
 </t>
   </si>
   <si>
@@ -1007,7 +1144,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AL54"/>
+  <dimension ref="A1:AL62"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="42.69921875" customWidth="true" bestFit="true"/>
@@ -1034,11 +1171,11 @@
     <col min="22" max="22" width="13.91796875" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="15.01171875" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="14.62890625" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="17.08203125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="61.64453125" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="82.14453125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="62.64453125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.07421875" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="17.98046875" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="16.2578125" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="34.578125" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="13.54296875" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="11.3203125" customWidth="true" bestFit="true" hidden="true"/>
     <col min="32" max="32" width="28.8359375" customWidth="true" bestFit="true" hidden="true"/>
@@ -1394,7 +1531,7 @@
       </c>
       <c r="E4" s="2"/>
       <c r="F4" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="G4" t="s" s="2">
         <v>84</v>
@@ -1509,10 +1646,10 @@
         <v>75</v>
       </c>
       <c r="I5" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="J5" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="K5" t="s" s="2">
         <v>98</v>
@@ -1523,9 +1660,7 @@
       <c r="M5" t="s" s="2">
         <v>100</v>
       </c>
-      <c r="N5" t="s" s="2">
-        <v>101</v>
-      </c>
+      <c r="N5" s="2"/>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
         <v>75</v>
@@ -1574,7 +1709,7 @@
         <v>75</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>76</v>
@@ -1586,32 +1721,32 @@
         <v>75</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>96</v>
+        <v>75</v>
       </c>
       <c r="AK5" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL5" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
     </row>
     <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
-        <v>75</v>
+        <v>103</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>75</v>
@@ -1658,55 +1793,57 @@
         <v>75</v>
       </c>
       <c r="X6" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y6" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z6" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA6" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB6" t="s" s="2">
         <v>108</v>
       </c>
-      <c r="Y6" s="2"/>
-      <c r="Z6" t="s" s="2">
+      <c r="AC6" t="s" s="2">
         <v>109</v>
       </c>
-      <c r="AA6" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB6" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC6" t="s" s="2">
-        <v>75</v>
-      </c>
       <c r="AD6" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE6" t="s" s="2">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AI6" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>96</v>
+        <v>112</v>
       </c>
       <c r="AK6" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL6" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
     </row>
     <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
@@ -1714,13 +1851,13 @@
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
-        <v>112</v>
+        <v>76</v>
       </c>
       <c r="G7" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="H7" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="I7" t="s" s="2">
         <v>75</v>
@@ -1729,7 +1866,7 @@
         <v>85</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>113</v>
+        <v>86</v>
       </c>
       <c r="L7" t="s" s="2">
         <v>114</v>
@@ -1737,7 +1874,9 @@
       <c r="M7" t="s" s="2">
         <v>115</v>
       </c>
-      <c r="N7" s="2"/>
+      <c r="N7" t="s" s="2">
+        <v>116</v>
+      </c>
       <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
         <v>75</v>
@@ -1774,29 +1913,31 @@
         <v>75</v>
       </c>
       <c r="AB7" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="AC7" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="AC7" t="s" s="2">
+        <v>75</v>
+      </c>
       <c r="AD7" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE7" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF7" t="s" s="2">
         <v>117</v>
       </c>
-      <c r="AF7" t="s" s="2">
-        <v>111</v>
-      </c>
       <c r="AG7" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH7" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AI7" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ7" t="s" s="2">
-        <v>118</v>
+        <v>96</v>
       </c>
       <c r="AK7" t="s" s="2">
         <v>75</v>
@@ -1807,10 +1948,10 @@
     </row>
     <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
@@ -1830,18 +1971,20 @@
         <v>75</v>
       </c>
       <c r="J8" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="K8" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="L8" t="s" s="2">
         <v>120</v>
       </c>
-      <c r="L8" t="s" s="2">
+      <c r="M8" t="s" s="2">
         <v>121</v>
       </c>
-      <c r="M8" t="s" s="2">
+      <c r="N8" t="s" s="2">
         <v>122</v>
       </c>
-      <c r="N8" s="2"/>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
         <v>75</v>
@@ -1902,13 +2045,13 @@
         <v>75</v>
       </c>
       <c r="AJ8" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AK8" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL8" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
     </row>
     <row r="9" hidden="true">
@@ -1920,14 +2063,14 @@
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>125</v>
+        <v>75</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G9" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="H9" t="s" s="2">
         <v>75</v>
@@ -1936,19 +2079,19 @@
         <v>75</v>
       </c>
       <c r="J9" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="K9" t="s" s="2">
+        <v>125</v>
+      </c>
+      <c r="L9" t="s" s="2">
         <v>126</v>
       </c>
-      <c r="L9" t="s" s="2">
+      <c r="M9" t="s" s="2">
         <v>127</v>
       </c>
-      <c r="M9" t="s" s="2">
+      <c r="N9" t="s" s="2">
         <v>128</v>
-      </c>
-      <c r="N9" t="s" s="2">
-        <v>129</v>
       </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
@@ -1998,41 +2141,41 @@
         <v>75</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH9" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AI9" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>131</v>
+        <v>96</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL9" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
     </row>
     <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
-        <v>133</v>
+        <v>75</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="G10" t="s" s="2">
         <v>77</v>
@@ -2041,26 +2184,24 @@
         <v>75</v>
       </c>
       <c r="I10" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="J10" t="s" s="2">
         <v>85</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="L10" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="M10" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="N10" t="s" s="2">
         <v>134</v>
       </c>
-      <c r="M10" t="s" s="2">
-        <v>135</v>
-      </c>
-      <c r="N10" t="s" s="2">
-        <v>129</v>
-      </c>
-      <c r="O10" t="s" s="2">
-        <v>136</v>
-      </c>
+      <c r="O10" s="2"/>
       <c r="P10" t="s" s="2">
         <v>75</v>
       </c>
@@ -2108,7 +2249,7 @@
         <v>75</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>76</v>
@@ -2120,21 +2261,21 @@
         <v>75</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>131</v>
+        <v>96</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL10" t="s" s="2">
-        <v>138</v>
+        <v>75</v>
       </c>
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -2142,10 +2283,10 @@
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="G11" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="H11" t="s" s="2">
         <v>75</v>
@@ -2157,15 +2298,17 @@
         <v>85</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>120</v>
+        <v>137</v>
       </c>
       <c r="L11" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="M11" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="N11" t="s" s="2">
         <v>140</v>
       </c>
-      <c r="M11" t="s" s="2">
-        <v>141</v>
-      </c>
-      <c r="N11" s="2"/>
       <c r="O11" s="2"/>
       <c r="P11" t="s" s="2">
         <v>75</v>
@@ -2190,13 +2333,13 @@
         <v>75</v>
       </c>
       <c r="X11" t="s" s="2">
-        <v>75</v>
+        <v>141</v>
       </c>
       <c r="Y11" t="s" s="2">
-        <v>75</v>
+        <v>142</v>
       </c>
       <c r="Z11" t="s" s="2">
-        <v>75</v>
+        <v>143</v>
       </c>
       <c r="AA11" t="s" s="2">
         <v>75</v>
@@ -2214,13 +2357,13 @@
         <v>75</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="AG11" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="AH11" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AI11" t="s" s="2">
         <v>75</v>
@@ -2237,10 +2380,10 @@
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2251,7 +2394,7 @@
         <v>76</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="H12" t="s" s="2">
         <v>75</v>
@@ -2263,15 +2406,17 @@
         <v>85</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>145</v>
-      </c>
-      <c r="N12" s="2"/>
+        <v>147</v>
+      </c>
+      <c r="N12" t="s" s="2">
+        <v>148</v>
+      </c>
       <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
         <v>75</v>
@@ -2296,13 +2441,13 @@
         <v>75</v>
       </c>
       <c r="X12" t="s" s="2">
-        <v>75</v>
+        <v>149</v>
       </c>
       <c r="Y12" t="s" s="2">
-        <v>75</v>
+        <v>150</v>
       </c>
       <c r="Z12" t="s" s="2">
-        <v>75</v>
+        <v>151</v>
       </c>
       <c r="AA12" t="s" s="2">
         <v>75</v>
@@ -2320,16 +2465,16 @@
         <v>75</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>142</v>
+        <v>152</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH12" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AI12" t="s" s="2">
-        <v>146</v>
+        <v>75</v>
       </c>
       <c r="AJ12" t="s" s="2">
         <v>96</v>
@@ -2343,10 +2488,10 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2363,22 +2508,22 @@
         <v>75</v>
       </c>
       <c r="I13" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="J13" t="s" s="2">
         <v>85</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>148</v>
+        <v>125</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -2428,7 +2573,7 @@
         <v>75</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>147</v>
+        <v>157</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>76</v>
@@ -2437,10 +2582,10 @@
         <v>84</v>
       </c>
       <c r="AI13" t="s" s="2">
-        <v>146</v>
+        <v>75</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AK13" t="s" s="2">
         <v>75</v>
@@ -2451,10 +2596,10 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2465,7 +2610,7 @@
         <v>76</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="H14" t="s" s="2">
         <v>75</v>
@@ -2474,19 +2619,19 @@
         <v>75</v>
       </c>
       <c r="J14" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>75</v>
+        <v>159</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>155</v>
+        <v>162</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -2512,13 +2657,11 @@
         <v>75</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y14" t="s" s="2">
-        <v>75</v>
-      </c>
+        <v>163</v>
+      </c>
+      <c r="Y14" s="2"/>
       <c r="Z14" t="s" s="2">
-        <v>75</v>
+        <v>164</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>75</v>
@@ -2536,13 +2679,13 @@
         <v>75</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>152</v>
+        <v>165</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AI14" t="s" s="2">
         <v>75</v>
@@ -2557,25 +2700,23 @@
         <v>75</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>156</v>
+        <v>166</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="C15" t="s" s="2">
-        <v>157</v>
-      </c>
+        <v>166</v>
+      </c>
+      <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
-        <v>84</v>
+        <v>167</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="H15" t="s" s="2">
         <v>85</v>
@@ -2587,13 +2728,13 @@
         <v>85</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>113</v>
+        <v>168</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>114</v>
+        <v>169</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>115</v>
+        <v>170</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -2632,19 +2773,17 @@
         <v>75</v>
       </c>
       <c r="AB15" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC15" t="s" s="2">
-        <v>75</v>
-      </c>
+        <v>171</v>
+      </c>
+      <c r="AC15" s="2"/>
       <c r="AD15" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE15" t="s" s="2">
-        <v>75</v>
+        <v>172</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>111</v>
+        <v>166</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>76</v>
@@ -2656,7 +2795,7 @@
         <v>75</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>118</v>
+        <v>173</v>
       </c>
       <c r="AK15" t="s" s="2">
         <v>75</v>
@@ -2667,10 +2806,10 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>158</v>
+        <v>174</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>119</v>
+        <v>174</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -2693,13 +2832,13 @@
         <v>75</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>120</v>
+        <v>98</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>121</v>
+        <v>99</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>122</v>
+        <v>100</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -2750,7 +2889,7 @@
         <v>75</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>123</v>
+        <v>101</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>76</v>
@@ -2773,14 +2912,14 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>159</v>
+        <v>175</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>124</v>
+        <v>175</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>125</v>
+        <v>103</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
@@ -2799,16 +2938,16 @@
         <v>75</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>126</v>
+        <v>104</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>127</v>
+        <v>105</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>128</v>
+        <v>106</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>129</v>
+        <v>107</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -2858,7 +2997,7 @@
         <v>75</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>130</v>
+        <v>111</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>76</v>
@@ -2870,7 +3009,7 @@
         <v>75</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>131</v>
+        <v>112</v>
       </c>
       <c r="AK17" t="s" s="2">
         <v>75</v>
@@ -2881,21 +3020,21 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>160</v>
+        <v>176</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>132</v>
+        <v>176</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>75</v>
+        <v>177</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H18" t="s" s="2">
         <v>75</v>
@@ -2907,16 +3046,20 @@
         <v>85</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>126</v>
+        <v>104</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>161</v>
+        <v>178</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="N18" s="2"/>
-      <c r="O18" s="2"/>
+        <v>179</v>
+      </c>
+      <c r="N18" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="O18" t="s" s="2">
+        <v>180</v>
+      </c>
       <c r="P18" t="s" s="2">
         <v>75</v>
       </c>
@@ -2964,7 +3107,7 @@
         <v>75</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>137</v>
+        <v>181</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>76</v>
@@ -2976,21 +3119,21 @@
         <v>75</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>131</v>
+        <v>112</v>
       </c>
       <c r="AK18" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="19">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>163</v>
+        <v>183</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>139</v>
+        <v>183</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3004,7 +3147,7 @@
         <v>84</v>
       </c>
       <c r="H19" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="I19" t="s" s="2">
         <v>75</v>
@@ -3013,13 +3156,13 @@
         <v>85</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>120</v>
+        <v>98</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>140</v>
+        <v>184</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>141</v>
+        <v>185</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -3028,7 +3171,7 @@
       </c>
       <c r="Q19" s="2"/>
       <c r="R19" t="s" s="2">
-        <v>157</v>
+        <v>75</v>
       </c>
       <c r="S19" t="s" s="2">
         <v>75</v>
@@ -3070,7 +3213,7 @@
         <v>75</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>139</v>
+        <v>183</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>84</v>
@@ -3091,12 +3234,12 @@
         <v>75</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>164</v>
+        <v>186</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>142</v>
+        <v>186</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3104,13 +3247,13 @@
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="G20" t="s" s="2">
         <v>84</v>
       </c>
       <c r="H20" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="I20" t="s" s="2">
         <v>75</v>
@@ -3119,13 +3262,13 @@
         <v>85</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>165</v>
+        <v>187</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>144</v>
+        <v>188</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>145</v>
+        <v>189</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -3176,7 +3319,7 @@
         <v>75</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>142</v>
+        <v>186</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>76</v>
@@ -3185,10 +3328,10 @@
         <v>84</v>
       </c>
       <c r="AI20" t="s" s="2">
-        <v>146</v>
+        <v>190</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>166</v>
+        <v>96</v>
       </c>
       <c r="AK20" t="s" s="2">
         <v>75</v>
@@ -3199,10 +3342,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>167</v>
+        <v>191</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>147</v>
+        <v>191</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3213,7 +3356,7 @@
         <v>76</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>75</v>
@@ -3225,16 +3368,16 @@
         <v>85</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>148</v>
+        <v>192</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>149</v>
+        <v>193</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>151</v>
+        <v>195</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -3284,7 +3427,7 @@
         <v>75</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>147</v>
+        <v>191</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>76</v>
@@ -3293,7 +3436,7 @@
         <v>84</v>
       </c>
       <c r="AI21" t="s" s="2">
-        <v>146</v>
+        <v>190</v>
       </c>
       <c r="AJ21" t="s" s="2">
         <v>75</v>
@@ -3307,10 +3450,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>168</v>
+        <v>196</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>152</v>
+        <v>196</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3333,16 +3476,16 @@
         <v>85</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>153</v>
+        <v>197</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>154</v>
+        <v>198</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>155</v>
+        <v>199</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -3392,7 +3535,7 @@
         <v>75</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>152</v>
+        <v>196</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>76</v>
@@ -3415,13 +3558,13 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>169</v>
+        <v>200</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>111</v>
+        <v>166</v>
       </c>
       <c r="C23" t="s" s="2">
-        <v>170</v>
+        <v>201</v>
       </c>
       <c r="D23" t="s" s="2">
         <v>75</v>
@@ -3443,13 +3586,13 @@
         <v>85</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>113</v>
+        <v>168</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>114</v>
+        <v>169</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>115</v>
+        <v>170</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -3500,7 +3643,7 @@
         <v>75</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>111</v>
+        <v>166</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>76</v>
@@ -3512,7 +3655,7 @@
         <v>75</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>118</v>
+        <v>173</v>
       </c>
       <c r="AK23" t="s" s="2">
         <v>75</v>
@@ -3523,10 +3666,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>171</v>
+        <v>202</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>119</v>
+        <v>174</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3549,13 +3692,13 @@
         <v>75</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>120</v>
+        <v>98</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>121</v>
+        <v>99</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>122</v>
+        <v>100</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -3606,7 +3749,7 @@
         <v>75</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>123</v>
+        <v>101</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>76</v>
@@ -3629,14 +3772,14 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>172</v>
+        <v>203</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>124</v>
+        <v>175</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>125</v>
+        <v>103</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
@@ -3655,16 +3798,16 @@
         <v>75</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>126</v>
+        <v>104</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>127</v>
+        <v>105</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>128</v>
+        <v>106</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>129</v>
+        <v>107</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
@@ -3714,7 +3857,7 @@
         <v>75</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>130</v>
+        <v>111</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>76</v>
@@ -3726,7 +3869,7 @@
         <v>75</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>131</v>
+        <v>112</v>
       </c>
       <c r="AK25" t="s" s="2">
         <v>75</v>
@@ -3737,10 +3880,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>173</v>
+        <v>204</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>132</v>
+        <v>176</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -3763,13 +3906,13 @@
         <v>85</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>126</v>
+        <v>104</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>161</v>
+        <v>205</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>162</v>
+        <v>206</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -3820,7 +3963,7 @@
         <v>75</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>137</v>
+        <v>181</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>76</v>
@@ -3832,7 +3975,7 @@
         <v>75</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>131</v>
+        <v>112</v>
       </c>
       <c r="AK26" t="s" s="2">
         <v>75</v>
@@ -3843,10 +3986,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>174</v>
+        <v>207</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>139</v>
+        <v>183</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -3869,13 +4012,13 @@
         <v>85</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>120</v>
+        <v>98</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>140</v>
+        <v>184</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>141</v>
+        <v>185</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -3884,7 +4027,7 @@
       </c>
       <c r="Q27" s="2"/>
       <c r="R27" t="s" s="2">
-        <v>170</v>
+        <v>201</v>
       </c>
       <c r="S27" t="s" s="2">
         <v>75</v>
@@ -3926,7 +4069,7 @@
         <v>75</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>139</v>
+        <v>183</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>84</v>
@@ -3949,10 +4092,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>175</v>
+        <v>208</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>142</v>
+        <v>186</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -3975,13 +4118,13 @@
         <v>85</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>165</v>
+        <v>209</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>144</v>
+        <v>188</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>145</v>
+        <v>189</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -4032,7 +4175,7 @@
         <v>75</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>142</v>
+        <v>186</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>76</v>
@@ -4041,10 +4184,10 @@
         <v>84</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>146</v>
+        <v>190</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>96</v>
+        <v>210</v>
       </c>
       <c r="AK28" t="s" s="2">
         <v>75</v>
@@ -4055,10 +4198,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>176</v>
+        <v>211</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>147</v>
+        <v>191</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4081,16 +4224,16 @@
         <v>85</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>148</v>
+        <v>192</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>149</v>
+        <v>193</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>151</v>
+        <v>195</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -4140,7 +4283,7 @@
         <v>75</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>147</v>
+        <v>191</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>76</v>
@@ -4149,7 +4292,7 @@
         <v>84</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>146</v>
+        <v>190</v>
       </c>
       <c r="AJ29" t="s" s="2">
         <v>75</v>
@@ -4163,10 +4306,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>177</v>
+        <v>212</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>152</v>
+        <v>196</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4192,13 +4335,13 @@
         <v>78</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>153</v>
+        <v>197</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>154</v>
+        <v>198</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>155</v>
+        <v>199</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -4248,7 +4391,7 @@
         <v>75</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>152</v>
+        <v>196</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>76</v>
@@ -4271,13 +4414,13 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>178</v>
+        <v>213</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>111</v>
+        <v>166</v>
       </c>
       <c r="C31" t="s" s="2">
-        <v>179</v>
+        <v>214</v>
       </c>
       <c r="D31" t="s" s="2">
         <v>75</v>
@@ -4299,13 +4442,13 @@
         <v>85</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>113</v>
+        <v>168</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>114</v>
+        <v>169</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>115</v>
+        <v>170</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -4356,7 +4499,7 @@
         <v>75</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>111</v>
+        <v>166</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>76</v>
@@ -4368,7 +4511,7 @@
         <v>75</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>118</v>
+        <v>173</v>
       </c>
       <c r="AK31" t="s" s="2">
         <v>75</v>
@@ -4379,10 +4522,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>180</v>
+        <v>215</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>119</v>
+        <v>174</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -4405,13 +4548,13 @@
         <v>75</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>120</v>
+        <v>98</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>121</v>
+        <v>99</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>122</v>
+        <v>100</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -4462,7 +4605,7 @@
         <v>75</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>123</v>
+        <v>101</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>76</v>
@@ -4485,14 +4628,14 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>181</v>
+        <v>216</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>124</v>
+        <v>175</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>125</v>
+        <v>103</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
@@ -4511,16 +4654,16 @@
         <v>75</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>126</v>
+        <v>104</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>127</v>
+        <v>105</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>128</v>
+        <v>106</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>129</v>
+        <v>107</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -4570,7 +4713,7 @@
         <v>75</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>130</v>
+        <v>111</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>76</v>
@@ -4582,7 +4725,7 @@
         <v>75</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>131</v>
+        <v>112</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>75</v>
@@ -4593,10 +4736,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>182</v>
+        <v>217</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>132</v>
+        <v>176</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -4619,13 +4762,13 @@
         <v>85</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>126</v>
+        <v>104</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>161</v>
+        <v>205</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>162</v>
+        <v>206</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -4676,7 +4819,7 @@
         <v>75</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>137</v>
+        <v>181</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>76</v>
@@ -4688,7 +4831,7 @@
         <v>75</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>131</v>
+        <v>112</v>
       </c>
       <c r="AK34" t="s" s="2">
         <v>75</v>
@@ -4699,10 +4842,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="B35" t="s" s="2">
         <v>183</v>
-      </c>
-      <c r="B35" t="s" s="2">
-        <v>139</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -4725,13 +4868,13 @@
         <v>85</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>120</v>
+        <v>98</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>140</v>
+        <v>184</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>141</v>
+        <v>185</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -4740,7 +4883,7 @@
       </c>
       <c r="Q35" s="2"/>
       <c r="R35" t="s" s="2">
-        <v>179</v>
+        <v>214</v>
       </c>
       <c r="S35" t="s" s="2">
         <v>75</v>
@@ -4782,7 +4925,7 @@
         <v>75</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>139</v>
+        <v>183</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>84</v>
@@ -4803,12 +4946,12 @@
         <v>75</v>
       </c>
     </row>
-    <row r="36" hidden="true">
+    <row r="36">
       <c r="A36" t="s" s="2">
-        <v>184</v>
+        <v>219</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>142</v>
+        <v>186</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -4816,13 +4959,13 @@
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="H36" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="I36" t="s" s="2">
         <v>75</v>
@@ -4831,13 +4974,13 @@
         <v>85</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>143</v>
+        <v>209</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>144</v>
+        <v>188</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>145</v>
+        <v>189</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -4888,7 +5031,7 @@
         <v>75</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>142</v>
+        <v>186</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>76</v>
@@ -4897,7 +5040,7 @@
         <v>84</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>146</v>
+        <v>190</v>
       </c>
       <c r="AJ36" t="s" s="2">
         <v>96</v>
@@ -4909,44 +5052,44 @@
         <v>75</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>185</v>
+        <v>220</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>147</v>
+        <v>191</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>186</v>
+        <v>75</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="H37" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I37" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J37" t="s" s="2">
         <v>85</v>
       </c>
-      <c r="I37" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J37" t="s" s="2">
-        <v>75</v>
-      </c>
       <c r="K37" t="s" s="2">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
@@ -4996,7 +5139,7 @@
         <v>75</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>147</v>
+        <v>191</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>76</v>
@@ -5005,7 +5148,7 @@
         <v>84</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>75</v>
+        <v>190</v>
       </c>
       <c r="AJ37" t="s" s="2">
         <v>75</v>
@@ -5014,15 +5157,15 @@
         <v>75</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>190</v>
+        <v>75</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>191</v>
+        <v>221</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>152</v>
+        <v>196</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5048,13 +5191,13 @@
         <v>78</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>153</v>
+        <v>197</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>154</v>
+        <v>198</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>155</v>
+        <v>199</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -5104,7 +5247,7 @@
         <v>75</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>152</v>
+        <v>196</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>76</v>
@@ -5127,13 +5270,13 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>192</v>
+        <v>222</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>111</v>
+        <v>166</v>
       </c>
       <c r="C39" t="s" s="2">
-        <v>193</v>
+        <v>223</v>
       </c>
       <c r="D39" t="s" s="2">
         <v>75</v>
@@ -5155,13 +5298,13 @@
         <v>85</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>113</v>
+        <v>168</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>114</v>
+        <v>169</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>115</v>
+        <v>170</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -5212,7 +5355,7 @@
         <v>75</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>111</v>
+        <v>166</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>76</v>
@@ -5224,7 +5367,7 @@
         <v>75</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>118</v>
+        <v>173</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>75</v>
@@ -5235,10 +5378,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>194</v>
+        <v>224</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>119</v>
+        <v>174</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -5261,13 +5404,13 @@
         <v>75</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>120</v>
+        <v>98</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>121</v>
+        <v>99</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>122</v>
+        <v>100</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -5318,7 +5461,7 @@
         <v>75</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>123</v>
+        <v>101</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>76</v>
@@ -5341,14 +5484,14 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>195</v>
+        <v>225</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>124</v>
+        <v>175</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>125</v>
+        <v>103</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
@@ -5367,16 +5510,16 @@
         <v>75</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>126</v>
+        <v>104</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>127</v>
+        <v>105</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>128</v>
+        <v>106</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>129</v>
+        <v>107</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -5426,7 +5569,7 @@
         <v>75</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>130</v>
+        <v>111</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>76</v>
@@ -5438,7 +5581,7 @@
         <v>75</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>131</v>
+        <v>112</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>75</v>
@@ -5449,10 +5592,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>196</v>
+        <v>226</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>132</v>
+        <v>176</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -5475,13 +5618,13 @@
         <v>85</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>126</v>
+        <v>104</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>161</v>
+        <v>205</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>162</v>
+        <v>206</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -5532,7 +5675,7 @@
         <v>75</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>137</v>
+        <v>181</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>76</v>
@@ -5544,7 +5687,7 @@
         <v>75</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>131</v>
+        <v>112</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>75</v>
@@ -5555,10 +5698,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>197</v>
+        <v>227</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>139</v>
+        <v>183</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -5581,13 +5724,13 @@
         <v>85</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>120</v>
+        <v>98</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>140</v>
+        <v>184</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>141</v>
+        <v>185</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -5596,7 +5739,7 @@
       </c>
       <c r="Q43" s="2"/>
       <c r="R43" t="s" s="2">
-        <v>193</v>
+        <v>223</v>
       </c>
       <c r="S43" t="s" s="2">
         <v>75</v>
@@ -5638,7 +5781,7 @@
         <v>75</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>139</v>
+        <v>183</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>84</v>
@@ -5659,12 +5802,12 @@
         <v>75</v>
       </c>
     </row>
-    <row r="44">
+    <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>198</v>
+        <v>228</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>142</v>
+        <v>186</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -5672,13 +5815,13 @@
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="H44" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="I44" t="s" s="2">
         <v>75</v>
@@ -5687,13 +5830,13 @@
         <v>85</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>144</v>
+        <v>188</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>145</v>
+        <v>189</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -5720,11 +5863,13 @@
         <v>75</v>
       </c>
       <c r="X44" t="s" s="2">
-        <v>200</v>
-      </c>
-      <c r="Y44" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="Y44" t="s" s="2">
+        <v>75</v>
+      </c>
       <c r="Z44" t="s" s="2">
-        <v>201</v>
+        <v>75</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>75</v>
@@ -5742,7 +5887,7 @@
         <v>75</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>142</v>
+        <v>186</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>76</v>
@@ -5751,7 +5896,7 @@
         <v>84</v>
       </c>
       <c r="AI44" t="s" s="2">
-        <v>146</v>
+        <v>190</v>
       </c>
       <c r="AJ44" t="s" s="2">
         <v>96</v>
@@ -5763,44 +5908,44 @@
         <v>75</v>
       </c>
     </row>
-    <row r="45" hidden="true">
+    <row r="45">
       <c r="A45" t="s" s="2">
-        <v>202</v>
+        <v>229</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>147</v>
+        <v>191</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>75</v>
+        <v>230</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="H45" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="I45" t="s" s="2">
         <v>75</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>148</v>
+        <v>231</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>149</v>
+        <v>232</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>150</v>
+        <v>233</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>151</v>
+        <v>233</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -5850,7 +5995,7 @@
         <v>75</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>147</v>
+        <v>191</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>76</v>
@@ -5859,7 +6004,7 @@
         <v>84</v>
       </c>
       <c r="AI45" t="s" s="2">
-        <v>146</v>
+        <v>75</v>
       </c>
       <c r="AJ45" t="s" s="2">
         <v>75</v>
@@ -5868,15 +6013,15 @@
         <v>75</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>75</v>
+        <v>234</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>203</v>
+        <v>235</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>152</v>
+        <v>196</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -5902,13 +6047,13 @@
         <v>78</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>153</v>
+        <v>197</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>154</v>
+        <v>198</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>155</v>
+        <v>199</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -5958,7 +6103,7 @@
         <v>75</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>152</v>
+        <v>196</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>76</v>
@@ -5981,23 +6126,23 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>204</v>
+        <v>236</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>111</v>
+        <v>166</v>
       </c>
       <c r="C47" t="s" s="2">
-        <v>205</v>
+        <v>237</v>
       </c>
       <c r="D47" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>85</v>
@@ -6009,13 +6154,13 @@
         <v>85</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>113</v>
+        <v>168</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>114</v>
+        <v>169</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>115</v>
+        <v>170</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -6066,7 +6211,7 @@
         <v>75</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>111</v>
+        <v>166</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>76</v>
@@ -6078,7 +6223,7 @@
         <v>75</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>118</v>
+        <v>173</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>75</v>
@@ -6089,10 +6234,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>206</v>
+        <v>238</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>119</v>
+        <v>174</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -6115,13 +6260,13 @@
         <v>75</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>120</v>
+        <v>98</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>121</v>
+        <v>99</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>122</v>
+        <v>100</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -6172,7 +6317,7 @@
         <v>75</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>123</v>
+        <v>101</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>76</v>
@@ -6195,14 +6340,14 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>207</v>
+        <v>239</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>124</v>
+        <v>175</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>125</v>
+        <v>103</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
@@ -6221,16 +6366,16 @@
         <v>75</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>126</v>
+        <v>104</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>127</v>
+        <v>105</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>128</v>
+        <v>106</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>129</v>
+        <v>107</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -6280,7 +6425,7 @@
         <v>75</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>130</v>
+        <v>111</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>76</v>
@@ -6292,7 +6437,7 @@
         <v>75</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>131</v>
+        <v>112</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>75</v>
@@ -6303,10 +6448,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>208</v>
+        <v>240</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>132</v>
+        <v>176</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -6329,13 +6474,13 @@
         <v>85</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>126</v>
+        <v>104</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>161</v>
+        <v>205</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>162</v>
+        <v>206</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -6386,7 +6531,7 @@
         <v>75</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>137</v>
+        <v>181</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>76</v>
@@ -6398,7 +6543,7 @@
         <v>75</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>131</v>
+        <v>112</v>
       </c>
       <c r="AK50" t="s" s="2">
         <v>75</v>
@@ -6409,10 +6554,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>209</v>
+        <v>241</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>139</v>
+        <v>183</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -6435,13 +6580,13 @@
         <v>85</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>120</v>
+        <v>98</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>140</v>
+        <v>184</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>141</v>
+        <v>185</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -6450,7 +6595,7 @@
       </c>
       <c r="Q51" s="2"/>
       <c r="R51" t="s" s="2">
-        <v>205</v>
+        <v>237</v>
       </c>
       <c r="S51" t="s" s="2">
         <v>75</v>
@@ -6492,7 +6637,7 @@
         <v>75</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>139</v>
+        <v>183</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>84</v>
@@ -6513,12 +6658,12 @@
         <v>75</v>
       </c>
     </row>
-    <row r="52" hidden="true">
+    <row r="52">
       <c r="A52" t="s" s="2">
-        <v>210</v>
+        <v>242</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>142</v>
+        <v>186</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -6526,13 +6671,13 @@
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="H52" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="I52" t="s" s="2">
         <v>75</v>
@@ -6541,13 +6686,13 @@
         <v>85</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>143</v>
+        <v>243</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>144</v>
+        <v>188</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>145</v>
+        <v>189</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -6574,13 +6719,11 @@
         <v>75</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y52" t="s" s="2">
-        <v>75</v>
-      </c>
+        <v>244</v>
+      </c>
+      <c r="Y52" s="2"/>
       <c r="Z52" t="s" s="2">
-        <v>75</v>
+        <v>245</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>75</v>
@@ -6598,7 +6741,7 @@
         <v>75</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>142</v>
+        <v>186</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>76</v>
@@ -6607,7 +6750,7 @@
         <v>84</v>
       </c>
       <c r="AI52" t="s" s="2">
-        <v>146</v>
+        <v>190</v>
       </c>
       <c r="AJ52" t="s" s="2">
         <v>96</v>
@@ -6619,12 +6762,12 @@
         <v>75</v>
       </c>
     </row>
-    <row r="53">
+    <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>211</v>
+        <v>246</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>147</v>
+        <v>191</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -6632,31 +6775,31 @@
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="H53" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I53" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J53" t="s" s="2">
         <v>85</v>
       </c>
-      <c r="I53" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J53" t="s" s="2">
-        <v>75</v>
-      </c>
       <c r="K53" t="s" s="2">
-        <v>212</v>
+        <v>192</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>213</v>
+        <v>193</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -6706,7 +6849,7 @@
         <v>75</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>147</v>
+        <v>191</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>76</v>
@@ -6715,24 +6858,24 @@
         <v>84</v>
       </c>
       <c r="AI53" t="s" s="2">
-        <v>75</v>
+        <v>190</v>
       </c>
       <c r="AJ53" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>214</v>
+        <v>75</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>215</v>
+        <v>75</v>
       </c>
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>216</v>
+        <v>247</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>152</v>
+        <v>196</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -6758,13 +6901,13 @@
         <v>78</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>153</v>
+        <v>197</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>154</v>
+        <v>198</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>155</v>
+        <v>199</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -6814,7 +6957,7 @@
         <v>75</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>152</v>
+        <v>196</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>76</v>
@@ -6835,8 +6978,864 @@
         <v>75</v>
       </c>
     </row>
+    <row r="55">
+      <c r="A55" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="B55" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="C55" t="s" s="2">
+        <v>249</v>
+      </c>
+      <c r="D55" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E55" s="2"/>
+      <c r="F55" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G55" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="H55" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="I55" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J55" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="K55" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="L55" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="M55" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="N55" s="2"/>
+      <c r="O55" s="2"/>
+      <c r="P55" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q55" s="2"/>
+      <c r="R55" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S55" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T55" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U55" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V55" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W55" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X55" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y55" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z55" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA55" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB55" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC55" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD55" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE55" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF55" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="AG55" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH55" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI55" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ55" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="AK55" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AL55" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="56" hidden="true">
+      <c r="A56" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="B56" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="C56" s="2"/>
+      <c r="D56" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E56" s="2"/>
+      <c r="F56" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G56" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H56" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I56" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J56" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K56" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="L56" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="M56" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="N56" s="2"/>
+      <c r="O56" s="2"/>
+      <c r="P56" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q56" s="2"/>
+      <c r="R56" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S56" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T56" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U56" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V56" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W56" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X56" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y56" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z56" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA56" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB56" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC56" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD56" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE56" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF56" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AG56" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH56" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI56" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ56" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AK56" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AL56" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="57" hidden="true">
+      <c r="A57" t="s" s="2">
+        <v>251</v>
+      </c>
+      <c r="B57" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="C57" s="2"/>
+      <c r="D57" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="E57" s="2"/>
+      <c r="F57" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G57" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="H57" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I57" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J57" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K57" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="L57" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="M57" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="N57" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="O57" s="2"/>
+      <c r="P57" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q57" s="2"/>
+      <c r="R57" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S57" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T57" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U57" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V57" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W57" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X57" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y57" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z57" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA57" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB57" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC57" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD57" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE57" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF57" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="AG57" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH57" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI57" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ57" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="AK57" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AL57" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="58" hidden="true">
+      <c r="A58" t="s" s="2">
+        <v>252</v>
+      </c>
+      <c r="B58" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="C58" s="2"/>
+      <c r="D58" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E58" s="2"/>
+      <c r="F58" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G58" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H58" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I58" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="J58" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="K58" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="L58" t="s" s="2">
+        <v>205</v>
+      </c>
+      <c r="M58" t="s" s="2">
+        <v>206</v>
+      </c>
+      <c r="N58" s="2"/>
+      <c r="O58" s="2"/>
+      <c r="P58" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q58" s="2"/>
+      <c r="R58" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S58" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T58" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U58" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V58" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W58" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X58" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y58" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z58" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA58" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB58" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC58" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD58" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE58" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF58" t="s" s="2">
+        <v>181</v>
+      </c>
+      <c r="AG58" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH58" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI58" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ58" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="AK58" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AL58" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="s" s="2">
+        <v>253</v>
+      </c>
+      <c r="B59" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="C59" s="2"/>
+      <c r="D59" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E59" s="2"/>
+      <c r="F59" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="G59" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H59" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="I59" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J59" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="K59" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="L59" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="M59" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="N59" s="2"/>
+      <c r="O59" s="2"/>
+      <c r="P59" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q59" s="2"/>
+      <c r="R59" t="s" s="2">
+        <v>249</v>
+      </c>
+      <c r="S59" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T59" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U59" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V59" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W59" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X59" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y59" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z59" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA59" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB59" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC59" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD59" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE59" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF59" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="AG59" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AH59" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI59" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ59" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="AK59" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AL59" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="60" hidden="true">
+      <c r="A60" t="s" s="2">
+        <v>254</v>
+      </c>
+      <c r="B60" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="C60" s="2"/>
+      <c r="D60" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E60" s="2"/>
+      <c r="F60" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G60" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H60" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I60" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J60" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="K60" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="L60" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="M60" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="N60" s="2"/>
+      <c r="O60" s="2"/>
+      <c r="P60" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q60" s="2"/>
+      <c r="R60" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S60" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T60" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U60" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V60" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W60" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X60" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y60" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z60" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA60" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB60" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC60" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD60" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE60" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF60" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="AG60" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH60" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI60" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="AJ60" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="AK60" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AL60" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="s" s="2">
+        <v>255</v>
+      </c>
+      <c r="B61" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="C61" s="2"/>
+      <c r="D61" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E61" s="2"/>
+      <c r="F61" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="G61" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H61" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="I61" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J61" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K61" t="s" s="2">
+        <v>256</v>
+      </c>
+      <c r="L61" t="s" s="2">
+        <v>257</v>
+      </c>
+      <c r="M61" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="N61" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="O61" s="2"/>
+      <c r="P61" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q61" s="2"/>
+      <c r="R61" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S61" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T61" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U61" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V61" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W61" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X61" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y61" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z61" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA61" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB61" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC61" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD61" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE61" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF61" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="AG61" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH61" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI61" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ61" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AK61" t="s" s="2">
+        <v>258</v>
+      </c>
+      <c r="AL61" t="s" s="2">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="62" hidden="true">
+      <c r="A62" t="s" s="2">
+        <v>260</v>
+      </c>
+      <c r="B62" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="C62" s="2"/>
+      <c r="D62" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E62" s="2"/>
+      <c r="F62" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G62" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="H62" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I62" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J62" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="K62" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="L62" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="M62" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="N62" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="O62" s="2"/>
+      <c r="P62" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q62" s="2"/>
+      <c r="R62" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S62" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T62" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U62" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V62" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W62" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X62" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y62" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z62" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA62" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB62" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC62" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD62" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE62" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF62" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="AG62" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH62" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI62" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ62" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="AK62" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AL62" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AL54">
+  <autoFilter ref="A1:AL62">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -6846,7 +7845,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI53">
+  <conditionalFormatting sqref="A2:AI61">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/StructureDefinition-access-check-eligibility-in.xlsx
+++ b/StructureDefinition-access-check-eligibility-in.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-04T22:54:52-04:00</t>
+    <t>2026-06-04T23:05:21-04:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-access-check-eligibility-in.xlsx
+++ b/StructureDefinition-access-check-eligibility-in.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.11</t>
+    <t>0.9.12</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-04T23:05:21-04:00</t>
+    <t>2026-06-10T23:08:55-04:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -781,7 +781,7 @@
     <t>required</t>
   </si>
   <si>
-    <t>https://dsacms.github.io/cmmi-access-model/ValueSet/ACCESSTrackVS|0.9.11</t>
+    <t>https://dsacms.github.io/cmmi-access-model/ValueSet/ACCESSTrackVS|0.9.12</t>
   </si>
   <si>
     <t>Parameters.parameter:track.resource</t>
@@ -814,7 +814,7 @@
     <t>Parameters.parameter:condition.resource</t>
   </si>
   <si>
-    <t xml:space="preserve">Condition {https://dsacms.github.io/cmmi-access-model/StructureDefinition/access-condition|0.9.11}
+    <t xml:space="preserve">Condition {https://dsacms.github.io/cmmi-access-model/StructureDefinition/access-condition|0.9.12}
 </t>
   </si>
   <si>
